--- a/result/factor_validation/factor_log.xlsx
+++ b/result/factor_validation/factor_log.xlsx
@@ -425,41 +425,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>训练开始</t>
+          <t>日期</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>训练结束</t>
+          <t>因子公式</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>验证开始</t>
+          <t>训练IC</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>验证结束</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>因子公式</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>训练IC</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>多空方向</t>
         </is>
@@ -468,34 +453,217 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2015-01-05</t>
+          <t>2024-01-31</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2022-11-29</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2022-12-28</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
+          <t>div(volume, high)</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0.0769</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>div(sqrt(open), low)</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2024-03-29</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>sub(volume, total_turnover)</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.0887</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2024-04-30</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>div(volume, total_turnover)</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.06909999999999999</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>div(volume, total_turnover)</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.0543</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>sub(mul(add(min(log(total_turnover), sub(high, 0.140)), abs(0.265)), 0.228), max(open, volume))</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.09710000000000001</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2024-07-31</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>sub(high, total_turnover)</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0.0606</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>sub(low, total_turnover)</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0.06270000000000001</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>sub(high, volume)</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0.0288</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2024-10-31</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>mul(log(high), low)</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0.0332</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2024-11-29</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>div(total_turnover, high)</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0.0102</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>2024-12-31</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>div(total_turnover, low)</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>-0.0232</v>
-      </c>
-      <c r="G2" t="n">
-        <v>-1</v>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>div(volume, max(high, volume))</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0.0296</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
